--- a/outputs/EMS upgrade output - fire_fighting_system_water_mist.xlsx
+++ b/outputs/EMS upgrade output - fire_fighting_system_water_mist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,16 +457,6 @@
           <t>Treatment Actions</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Reporting Question ID</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Treatment Action Type</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -476,47 +466,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Water Mist Pump Failure *</t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressurize water from reservoir into the distribution piping network at required flow and pressure for mist generation </t>
+          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Worn impeller or diffuser reduces pump discharge pressure below design specification </t>
+          <t xml:space="preserve">Cylinder body dented or bulging due to mechanical stress, potential for rupture </t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump discharge pressure at design specification? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Cylinder visual inspection for shape distortion [Y/N]; Cylinder hydrostatic test performed per interval [Y/N] </t>
         </is>
       </c>
     </row>
@@ -528,22 +508,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Water Mist Pump Failure *</t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressurize water from reservoir into the distribution piping network at required flow and pressure for mist generation </t>
+          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -553,22 +533,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internal casing corrosion degrades hydraulic efficiency, reducing pressure output </t>
+          <t xml:space="preserve">Water/gas mixture leakage from cylinder wall or valve connection </t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump casing thickness verified by NDT? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Cylinder external visual corrosion inspection performed [Y/N]; Cylinder wall thickness measured within limit [Y/N] </t>
         </is>
       </c>
     </row>
@@ -580,47 +550,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Water Mist Pump Failure *</t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressurize water from reservoir into the distribution piping network at required flow and pressure for mist generation </t>
+          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erosive wear of impeller vanes reduces head capacity </t>
+          <t xml:space="preserve">Stress crack in cylinder wall leads to leakage </t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impeller condition verified during overhaul? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Cylinder surface crack detection performed [Y/N]; Cylinder certification/requalification within interval [Y/N] </t>
         </is>
       </c>
     </row>
@@ -632,47 +592,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Water Mist Pump Failure *</t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressurize water from reservoir into the distribution piping network at required flow and pressure for mist generation </t>
+          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump-to-motor shaft misalignment induces excessive vibration </t>
+          <t xml:space="preserve">Catastrophic cylinder burst or rupture </t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump/motor alignment verified? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Cylinder pressure relief device inspected [Y/N]; Cylinder within life cycle replacement schedule [Y/N] </t>
         </is>
       </c>
     </row>
@@ -684,47 +634,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Water Mist Pump Failure *</t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressurize water from reservoir into the distribution piping network at required flow and pressure for mist generation </t>
+          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft fatigue cracking generates vibration </t>
+          <t xml:space="preserve">Water quality or gas purity compromised affecting mist performance </t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibration analysis performed? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Water sample tested per quality specification [Y/N]; Cylinder gas purity verified [Y/N] </t>
         </is>
       </c>
     </row>
@@ -736,47 +676,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Water Mist Pump Failure *</t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressurize water from reservoir into the distribution piping network at required flow and pressure for mist generation </t>
+          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">3.4 Out of adjustment </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose foundation bolts allow pump movement generating vibration </t>
+          <t xml:space="preserve">Cylinder pressure not at design setpoint </t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foundation bolts torque checked? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Cylinder pressure gauge reading within acceptable range [Y/N]; Pressure recorded vs specification [Y/N] </t>
         </is>
       </c>
     </row>
@@ -788,47 +718,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Water Mist Pump Failure *</t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressurize water from reservoir into the distribution piping network at required flow and pressure for mist generation </t>
+          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1 Cavitation </t>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cavitation bubbles collapse causing noise and impeller pitting </t>
+          <t xml:space="preserve">Pressure drop from temperature fluctuation affecting system readiness </t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump suction pressure above NPSHR? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Ambient temperature in cylinder storage area within acceptable range [Y/N]; Cylinder temperature recorded [Y/N] </t>
         </is>
       </c>
     </row>
@@ -840,22 +760,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Water Mist Pump Failure *</t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressurize water from reservoir into the distribution piping network at required flow and pressure for mist generation </t>
+          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -865,22 +785,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Worn bearing rolling elements generate abnormal noise </t>
+          <t xml:space="preserve">Valve seat wear allows slow gas leakage reducing pressure </t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing acoustic analysis normal? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Cylinder valve seat leakage test performed [Y/N]; Cylinder valve replaced if leaking [Y/N] </t>
         </is>
       </c>
     </row>
@@ -892,47 +802,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Water Mist Pump Failure *</t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressurize water from reservoir into the distribution piping network at required flow and pressure for mist generation </t>
+          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue in coupling components creates abnormal sound </t>
+          <t xml:space="preserve">External corrosion reduces structural integrity over time </t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling condition verified during inspection? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Cylinder surface condition acceptable (no pitting/scaling) [Y/N]; Cylinder protective coating intact [Y/N] </t>
         </is>
       </c>
     </row>
@@ -944,47 +844,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Water Mist Pump Failure *</t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressurize water from reservoir into the distribution piping network at required flow and pressure for mist generation </t>
+          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing seizure from inadequate lubrication generates heat </t>
+          <t xml:space="preserve">Damage from impact or mishandling </t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing lubricant level and condition verified? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Cylinder body free of dents and distortion [Y/N]; Cylinder mounting brackets secure and undamaged [Y/N] </t>
         </is>
       </c>
     </row>
@@ -996,47 +886,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Water Mist Pump Failure *</t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressurize water from reservoir into the distribution piping network at required flow and pressure for mist generation </t>
+          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Worn mechanical seal face generates friction heat </t>
+          <t xml:space="preserve">Fatigue cracking at mounting points or valve neck connection </t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanical seal temperature within limits? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Cylinder mounting bracket inspection for cracks [Y/N]; Cylinder neck thread inspection performed [Y/N] </t>
         </is>
       </c>
     </row>
@@ -1048,47 +928,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Water Mist Pump Failure *</t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressurize water from reservoir into the distribution piping network at required flow and pressure for mist generation </t>
+          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.1 Blockage/plugged </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recirculation path blockage causes internal heat buildup in pump casing </t>
+          <t xml:space="preserve">Crack propagation from corrosion or fatigue weakens cylinder wall </t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump casing temperature monitored? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Cylinder visual/dye-penetrant inspection for cracks [Y/N]; Cylinder replaced if structural defect found [Y/N] </t>
         </is>
       </c>
     </row>
@@ -1100,47 +970,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Water Mist Pump Failure *</t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressurize water from reservoir into the distribution piping network at required flow and pressure for mist generation </t>
+          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">FTF - Failure to function on demand </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Casing corrosion pit penetrates wall causing water loss </t>
+          <t xml:space="preserve">Outlet valve blocked by debris preventing system discharge </t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump casing free of active corrosion? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Cylinder outlet valve function test performed [Y/N]; Cylinder discharge test on schedule [Y/N] </t>
         </is>
       </c>
     </row>
@@ -1152,47 +1012,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Water Mist Pump Failure *</t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressurize water from reservoir into the distribution piping network at required flow and pressure for mist generation </t>
+          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">FTF - Failure to function on demand </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">1.6 Sticking </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket compression set causes flange joint water leak </t>
+          <t xml:space="preserve">Valve mechanism stuck preventing discharge </t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flange bolts torque and gasket condition verified? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Cylinder valve manual operation test performed [Y/N]; Cylinder valve mechanism lubricated [Y/N] </t>
         </is>
       </c>
     </row>
@@ -1204,47 +1054,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Water Mist Pump Failure *</t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressurize water from reservoir into the distribution piping network at required flow and pressure for mist generation </t>
+          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOO - Low output </t>
+          <t xml:space="preserve">FTF - Failure to function on demand </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eroded impeller reduces pump flow capacity </t>
+          <t xml:space="preserve">Corrosion seizes valve mechanism </t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump flow rate measured at design RPM? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Cylinder valve disassembled and inspected per interval [Y/N]; Cylinder replaced if valve seized [Y/N] </t>
         </is>
       </c>
     </row>
@@ -1256,22 +1096,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Water Mist Pump Failure *</t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressurize water from reservoir into the distribution piping network at required flow and pressure for mist generation </t>
+          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOO - Low output </t>
+          <t xml:space="preserve">FTF - Failure to function on demand </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1281,22 +1121,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Worn wear rings increase internal recirculation reducing net output </t>
+          <t xml:space="preserve">Valve seat wear causes internal bypass reducing discharge pressure </t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump internal clearances verified? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Cylinder valve seat condition inspected [Y/N]; Cylinder replaced if valve seat worn [Y/N] </t>
         </is>
       </c>
     </row>
@@ -1308,47 +1138,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Water Mist Pump Failure *</t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressurize water from reservoir into the distribution piping network at required flow and pressure for mist generation </t>
+          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOO - Low output </t>
+          <t xml:space="preserve">NOO - No output </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.1 Blockage/plugged </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suction strainer partial blockage restricts inlet flow to pump </t>
+          <t xml:space="preserve">Cylinder empty from undetected leakage through contamination-induced seal failure </t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suction strainer clean and unobstructed? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Cylinder weight verification performed [Y/N]; Cylinder liquid level indicator inspected [Y/N] </t>
         </is>
       </c>
     </row>
@@ -1360,47 +1180,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Piping System Failure *</t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transport pressurized water from pump station to all nozzle arrays throughout the protected area </t>
+          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">NOO - No output </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">3.4 Out of adjustment </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion pinhole in pipe wall causes water spray loss </t>
+          <t xml:space="preserve">Insufficient pressure prevents discharge </t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping thickness verified by UT inspection? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Cylinder pressure gauged within acceptable range [Y/N]; Cylinder recharged if under pressure [Y/N] </t>
         </is>
       </c>
     </row>
@@ -1412,47 +1222,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Piping System Failure *</t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transport pressurized water from pump station to all nozzle arrays throughout the protected area </t>
+          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">NOO - No output </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue crack at weld joint causes water leak </t>
+          <t xml:space="preserve">Valve neck fracture prevents any discharge </t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weld inspection performed by MPI? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Cylinder valve area visual inspection for cracks [Y/N]; Cylinder replaced if neck damaged [Y/N] </t>
         </is>
       </c>
     </row>
@@ -1464,47 +1264,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Piping System Failure *</t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transport pressurized water from pump station to all nozzle arrays throughout the protected area </t>
+          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">NOO - No output </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">1.6 Sticking </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanical impact damage deforms pipe creating leak path </t>
+          <t xml:space="preserve">Valve stuck in closed position preventing discharge </t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping free of mechanical damage? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Cylinder valve operation test performed [Y/N]; Cylinder valve freed or replaced [Y/N] </t>
         </is>
       </c>
     </row>
@@ -1516,47 +1306,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Piping System Failure *</t>
+          <t>Nozzle Failure</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transport pressurized water from pump station to all nozzle arrays throughout the protected area </t>
+          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generalized wall thinning reduces pipe pressure rating below system demand </t>
+          <t xml:space="preserve">Nozzle orifice blocked by debris or scale from piping </t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pipe wall thickness minimum verified by NDT? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Nozzle visual inspection for obstruction [Y/N]; Nozzle flow test performed within tolerance [Y/N] </t>
         </is>
       </c>
     </row>
@@ -1568,47 +1348,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Piping System Failure *</t>
+          <t>Nozzle Failure</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transport pressurized water from pump station to all nozzle arrays throughout the protected area </t>
+          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pipe support corrosion causes sagging and excessive stress on pipe joints </t>
+          <t xml:space="preserve">Corrosion products obstruct nozzle orifice </t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pipe supports condition verified? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Nozzle material corrosion condition inspected [Y/N]; Nozzle replacement per interval program [Y/N] </t>
         </is>
       </c>
     </row>
@@ -1620,47 +1390,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Piping System Failure *</t>
+          <t>Nozzle Failure</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transport pressurized water from pump station to all nozzle arrays throughout the protected area </t>
+          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">2.3 Erosion </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freeze damage causes pipe rupture in exposed sections </t>
+          <t xml:space="preserve">Droplet erosion enlarges/mis-shapes orifice affecting mist quality </t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping heat tracing functional where installed? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Nozzle discharge pattern tested per specification [Y/N]; Nozzle bore dimensions measured within limit [Y/N] </t>
         </is>
       </c>
     </row>
@@ -1672,17 +1432,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Piping System Failure *</t>
+          <t>Nozzle Failure</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transport pressurized water from pump station to all nozzle arrays throughout the protected area </t>
+          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1692,27 +1452,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debris accumulation from construction debris blocks pipe cross-section </t>
+          <t xml:space="preserve">Mechanical wear from aging/cycling degrades orifice geometry </t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping flushed and clear after installation/modification? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Nozzle dimensional check performed [Y/N]; Nozzle replacement scheduled [Y/N] </t>
         </is>
       </c>
     </row>
@@ -1724,47 +1474,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Piping System Failure *</t>
+          <t>Nozzle Failure</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transport pressurized water from pump station to all nozzle arrays throughout the protected area </t>
+          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion scale buildup restricts internal diameter </t>
+          <t xml:space="preserve">Droplet size distribution out of spec due to partial blockage </t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping internal condition verified by scope? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Nozzle spray pattern observed and acceptable [Y/N]; Nozzle flow rate verified per datasheet [Y/N] </t>
         </is>
       </c>
     </row>
@@ -1776,17 +1516,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Piping System Failure *</t>
+          <t>Nozzle Failure</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transport pressurized water from pump station to all nozzle arrays throughout the protected area </t>
+          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1801,22 +1541,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internal corrosion roughness increases friction loss, reducing downstream pressure </t>
+          <t xml:space="preserve">Orifice enlargement from corrosion alters spray characteristics </t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flow test results compare to baseline? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Nozzle corrosion grade condition acceptable [Y/N]; Nozzle inspected per manufacturer specification [Y/N] </t>
         </is>
       </c>
     </row>
@@ -1828,17 +1558,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Piping System Failure *</t>
+          <t>Nozzle Failure</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transport pressurized water from pump station to all nozzle arrays throughout the protected area </t>
+          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1848,27 +1578,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">2.3 Erosion </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial debris obstruction causes section pressure deviation from design </t>
+          <t xml:space="preserve">Erosive wear changes spray angle or distribution pattern </t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section pressure gauges reading within expected range? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Nozzle spray test conducted and passed [Y/N]; Nozzle replacement on condition [Y/N] </t>
         </is>
       </c>
     </row>
@@ -1880,17 +1600,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Piping System Failure *</t>
+          <t>Nozzle Failure</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transport pressurized water from pump station to all nozzle arrays throughout the protected area </t>
+          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1900,27 +1620,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pipe support failure alters routing causing flow restriction </t>
+          <t xml:space="preserve">Paint or coating overspray obstructs nozzle opening </t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pipe support alignment verified? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Nozzle visual check for external contamination [Y/N]; Nozzle protective cap in place (where fitted) [Y/N] </t>
         </is>
       </c>
     </row>
@@ -1932,47 +1642,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Piping System Failure *</t>
+          <t>Nozzle Failure</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transport pressurized water from pump station to all nozzle arrays throughout the protected area </t>
+          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose pipe clamps allow pipe movement during flow </t>
+          <t xml:space="preserve">Physical damage from impact, heat, or corrosion </t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pipe clamps secure and tight? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Nozzle body free of cracks and deformation [Y/N]; Nozzle mounting secure [Y/N] </t>
         </is>
       </c>
     </row>
@@ -1984,47 +1684,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Piping System Failure *</t>
+          <t>Nozzle Failure</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transport pressurized water from pump station to all nozzle arrays throughout the protected area </t>
+          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Water hammer fatigue causes pipe movement and vibration </t>
+          <t xml:space="preserve">Corrosion weakens nozzle body structure </t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Surge suppression devices functional? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Nozzle condition grade acceptable [Y/N]; Nozzle replaced per maintenance schedule [Y/N] </t>
         </is>
       </c>
     </row>
@@ -2036,47 +1726,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Piping System Failure *</t>
+          <t>Nozzle Failure</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transport pressurized water from pump station to all nozzle arrays throughout the protected area </t>
+          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjacent equipment vibration transmitted to piping system </t>
+          <t xml:space="preserve">Fatigue cracking at nozzle-to-piping connection due to vibration </t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pipe vibration dampers condition verified? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Nozzle connection inspected for cracks [Y/N]; Nozzle support bracket secure [Y/N] </t>
         </is>
       </c>
     </row>
@@ -2088,47 +1768,37 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Piping System Failure *</t>
+          <t>Nozzle Failure</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transport pressurized water from pump station to all nozzle arrays throughout the protected area </t>
+          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRD - Breakdown </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catastrophic pipe rupture from overpressure event </t>
+          <t xml:space="preserve">Thread wear on nozzle body from repeated assembly/disassembly </t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRD tested and functional? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Nozzle thread condition inspected [Y/N]; Nozzle replaced if thread worn [Y/N] </t>
         </is>
       </c>
     </row>
@@ -2140,47 +1810,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Piping System Failure *</t>
+          <t>Nozzle Failure</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transport pressurized water from pump station to all nozzle arrays throughout the protected area </t>
+          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRD - Breakdown </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue failure from repeated pressure surges </t>
+          <t xml:space="preserve">Water leak at nozzle-to-piping threaded connection from corrosion </t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">System pressure surge cycles recorded? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Nozzle connection inspected for leakage [Y/N]; Joint seals/gaskets condition checked [Y/N] </t>
         </is>
       </c>
     </row>
@@ -2192,7 +1852,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2202,37 +1862,27 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge pressurized water as fine mist droplets for effective fire suppression by cooling and oxygen displacement </t>
+          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">1.5 Looseness </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sediment or debris lodges in nozzle orifice blocking flow </t>
+          <t xml:space="preserve">Nozzle not fully tightened or seal degraded </t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle flushed and free of debris? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Nozzle torque check performed [Y/N]; Nozzle seal/gasket replaced if degraded [Y/N] </t>
         </is>
       </c>
     </row>
@@ -2244,7 +1894,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2254,37 +1904,27 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge pressurized water as fine mist droplets for effective fire suppression by cooling and oxygen displacement </t>
+          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion scale breaks loose from pipe interior and blocks nozzle opening </t>
+          <t xml:space="preserve">Thread damage from overtightening or cross-threading causes leak </t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle internal passage clear of scale? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Nozzle thread condition inspected [Y/N]; Nozzle replaced if damaged [Y/N] </t>
         </is>
       </c>
     </row>
@@ -2296,7 +1936,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2306,37 +1946,27 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge pressurized water as fine mist droplets for effective fire suppression by cooling and oxygen displacement </t>
+          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erosion debris from pipe interior lodges inside nozzle </t>
+          <t xml:space="preserve">Thread wear from repeated assembly/disassembly causes leak path </t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Downstream strainer effective at protecting nozzles? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Nozzle replacement scheduled based on wear assessment [Y/N]; Spare nozzle available [Y/N] </t>
         </is>
       </c>
     </row>
@@ -2348,7 +1978,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2358,37 +1988,27 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge pressurized water as fine mist droplets for effective fire suppression by cooling and oxygen displacement </t>
+          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">FTF - Failure to function on demand </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orifice wear changes spray droplet size distribution affecting suppression efficiency </t>
+          <t xml:space="preserve">Nozzle fails to discharge due to obstruction from debris </t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spray pattern tested per design specification? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">System activation test performed - nozzle discharge verified [Y/N]; Nozzle obstruction check performed [Y/N] </t>
         </is>
       </c>
     </row>
@@ -2400,7 +2020,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2410,37 +2030,27 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge pressurized water as fine mist droplets for effective fire suppression by cooling and oxygen displacement </t>
+          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">FTF - Failure to function on demand </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erosion enlarges nozzle orifice reducing mist quality and coverage area </t>
+          <t xml:space="preserve">Corrosion seizes nozzle internal moving parts (fusible link or release mechanism) </t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle flow rate within acceptable limits? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Nozzle movement/freedom test performed [Y/N]; Nozzle replaced if seized [Y/N] </t>
         </is>
       </c>
     </row>
@@ -2452,7 +2062,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2462,37 +2072,27 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge pressurized water as fine mist droplets for effective fire suppression by cooling and oxygen displacement </t>
+          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">FTF - Failure to function on demand </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">1.6 Sticking </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion roughens internal surface altering spray pattern </t>
+          <t xml:space="preserve">Paint or coating buildup prevents nozzle activation </t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle internal condition verified by inspection? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Nozzle activation test performed per schedule [Y/N]; Nozzle protective cap condition verified [Y/N] </t>
         </is>
       </c>
     </row>
@@ -2504,7 +2104,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2514,37 +2114,27 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge pressurized water as fine mist droplets for effective fire suppression by cooling and oxygen displacement </t>
+          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">FTF - Failure to function on demand </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle body corrosion weakens structural integrity under system pressure </t>
+          <t xml:space="preserve">Mechanical damage (impact) deforms nozzle preventing discharge </t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle body free of corrosion? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Nozzle physical condition inspected [Y/N]; Nozzle replaced if damaged [Y/N] </t>
         </is>
       </c>
     </row>
@@ -2556,47 +2146,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Piping Failure</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge pressurized water as fine mist droplets for effective fire suppression by cooling and oxygen displacement </t>
+          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanical impact deforms nozzle body </t>
+          <t xml:space="preserve">Pinhole leak from external or internal corrosion </t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle body free of dents/damage? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Piping visual inspection for corrosion damage performed [Y/N]; Piping wall thickness (UT) measured within limit [Y/N] </t>
         </is>
       </c>
     </row>
@@ -2608,47 +2188,37 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Piping Failure</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge pressurized water as fine mist droplets for effective fire suppression by cooling and oxygen displacement </t>
+          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thread breakage at nozzle mounting connection </t>
+          <t xml:space="preserve">Vibration-induced fatigue crack at supports or fittings </t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle securely attached to piping? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Piping supports/brackets inspected for damage [Y/N]; Piping vibration dampeners effective [Y/N] </t>
         </is>
       </c>
     </row>
@@ -2660,17 +2230,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Piping Failure</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge pressurized water as fine mist droplets for effective fire suppression by cooling and oxygen displacement </t>
+          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2685,22 +2255,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose nozzle-to-pipe connection leaks water </t>
+          <t xml:space="preserve">Flange or fitting loosened causing leak at joint </t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle connection tightness verified? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Flange bolts torque checked [Y/N]; Joint gaskets inspected for condition [Y/N] </t>
         </is>
       </c>
     </row>
@@ -2712,17 +2272,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Piping Failure</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge pressurized water as fine mist droplets for effective fire suppression by cooling and oxygen displacement </t>
+          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2732,27 +2292,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thread corrosion degrades seal causing leak at nozzle joint </t>
+          <t xml:space="preserve">Pipe rupture due to overpressure or freeze damage </t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle thread condition verified? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Piping pressure test performed per interval [Y/N]; Freeze protection (trace heating/insulation) operational [Y/N] </t>
         </is>
       </c>
     </row>
@@ -2764,47 +2314,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Piping Failure</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge pressurized water as fine mist droplets for effective fire suppression by cooling and oxygen displacement </t>
+          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eroded orifice produces altered spray sound during operation </t>
+          <t xml:space="preserve">Sediment or scale buildup in piping restricts flow </t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle operation verified by function test? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Piping flush performed per maintenance schedule [Y/N]; System strainer inspected clean [Y/N] </t>
         </is>
       </c>
     </row>
@@ -2816,47 +2356,37 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Piping Failure</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge pressurized water as fine mist droplets for effective fire suppression by cooling and oxygen displacement </t>
+          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1 Cavitation </t>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cavitation at nozzle orifice creates abnormal spray noise </t>
+          <t xml:space="preserve">Foreign object or construction debris obstructs piping </t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">System pressure at nozzle within design range? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Piping borescope inspection performed for obstructions [Y/N]; Flow test performed and acceptable [Y/N] </t>
         </is>
       </c>
     </row>
@@ -2868,47 +2398,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Piping Failure</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge pressurized water as fine mist droplets for effective fire suppression by cooling and oxygen displacement </t>
+          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue crack in nozzle body creates whistling sound </t>
+          <t xml:space="preserve">Corrosion buildup (tuberculation) narrows pipe bore restricting flow </t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle body condition verified? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Piping internal condition assessed per schedule [Y/N]; Piping replacement on condition [Y/N] </t>
         </is>
       </c>
     </row>
@@ -2920,47 +2440,37 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Valve Failure</t>
+          <t>Piping Failure</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate water mist system sections for maintenance, testing, and controlled water release </t>
+          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTO - Failure to open on demand </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking </t>
+          <t xml:space="preserve">2.3 Erosion </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve stem corrosion prevents rotation to open position </t>
+          <t xml:space="preserve">Erosion debris trapped at restrictions creates partial blockages </t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve stem lubricated and free moving? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Piping internal inspection at low points performed [Y/N]; Piping drain/flush valve exercised [Y/N] </t>
         </is>
       </c>
     </row>
@@ -2972,47 +2482,37 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Valve Failure</t>
+          <t>Piping Failure</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate water mist system sections for maintenance, testing, and controlled water release </t>
+          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTO - Failure to open on demand </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debris jammed in valve seat prevents gate movement </t>
+          <t xml:space="preserve">Internal corrosion increases surface roughness reducing flow capacity </t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve full stroke cycle tested? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Flow test conducted within acceptable limit [Y/N]; Piping internal corrosion assessment performed [Y/N] </t>
         </is>
       </c>
     </row>
@@ -3024,47 +2524,37 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Valve Failure</t>
+          <t>Piping Failure</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate water mist system sections for maintenance, testing, and controlled water release </t>
+          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTO - Failure to open on demand </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.3 Erosion </t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internal corrosion binds valve operating mechanism </t>
+          <t xml:space="preserve">Erosion at bends or restrictions alters flow characteristics </t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve actuator connection free of corrosion? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Piping wall thickness at bends measured [Y/N]; Piping replacement scheduled based on UT readings [Y/N] </t>
         </is>
       </c>
     </row>
@@ -3076,47 +2566,37 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Valve Failure</t>
+          <t>Piping Failure</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate water mist system sections for maintenance, testing, and controlled water release </t>
+          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTC - Failure to close on demand </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Worn valve seat prevents tight seal when closed </t>
+          <t xml:space="preserve">Scale/deposit buildup increases friction loss reducing flow </t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve seat condition verified during maintenance? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Water quality test performed - acceptable [Y/N]; Pipe cleaning/flush performed per interval [Y/N] </t>
         </is>
       </c>
     </row>
@@ -3128,47 +2608,37 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Valve Failure</t>
+          <t>Piping Failure</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate water mist system sections for maintenance, testing, and controlled water release </t>
+          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTC - Failure to close on demand </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scale buildup on guide surface prevents full closure </t>
+          <t xml:space="preserve">Kinked or crushed pipe reduces cross-section area </t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve internal surfaces cleaned? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Piping visual inspection for kinks/flattened sections [Y/N]; Piping replaced if deformed [Y/N] </t>
         </is>
       </c>
     </row>
@@ -3180,47 +2650,37 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Valve Failure</t>
+          <t>Piping Failure</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate water mist system sections for maintenance, testing, and controlled water release </t>
+          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTC - Failure to close on demand </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distorted valve gate prevents proper sealing </t>
+          <t xml:space="preserve">External corrosion weakens pipe wall structural integrity </t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve gate condition verified? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Piping external surface condition acceptable [Y/N]; Protective coating condition acceptable [Y/N] </t>
         </is>
       </c>
     </row>
@@ -3232,47 +2692,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Valve Failure</t>
+          <t>Piping Failure</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate water mist system sections for maintenance, testing, and controlled water release </t>
+          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Worn packing/stem seal leaks water externally </t>
+          <t xml:space="preserve">Dents or mechanical damage from impact </t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve packing condition and adjustment verified? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Piping inspection for mechanical damage performed [Y/N]; Piping supports and clamps inspected [Y/N] </t>
         </is>
       </c>
     </row>
@@ -3284,47 +2734,37 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Valve Failure</t>
+          <t>Piping Failure</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate water mist system sections for maintenance, testing, and controlled water release </t>
+          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve body corrosion pit penetrates wall </t>
+          <t xml:space="preserve">Mechanical fatigue at support points from vibration </t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve body free of corrosion damage? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Piping hanger/support condition inspected [Y/N]; Pipe clamp torque verified [Y/N] </t>
         </is>
       </c>
     </row>
@@ -3336,47 +2776,37 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Valve Failure</t>
+          <t>Piping Failure</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate water mist system sections for maintenance, testing, and controlled water release </t>
+          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flange gasket failure causes joint leak at valve </t>
+          <t xml:space="preserve">Complete pipe fracture due to overstress or corrosion </t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve flange bolts torque verified? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Piping pressure integrity test performed [Y/N]; Piping replaced if crack or fracture found [Y/N] </t>
         </is>
       </c>
     </row>
@@ -3388,47 +2818,37 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Valve Failure</t>
+          <t>Piping Failure</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate water mist system sections for maintenance, testing, and controlled water release </t>
+          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">FTF - Failure to function on demand </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eroded valve trim alters flow characteristics </t>
+          <t xml:space="preserve">Obstruction prevents water flow during activation </t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve Cv performance verified? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">System discharge test performed - flow verified to all zones [Y/N]; Piping section isolation tested [Y/N] </t>
         </is>
       </c>
     </row>
@@ -3440,47 +2860,37 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Valve Failure</t>
+          <t>Piping Failure</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate water mist system sections for maintenance, testing, and controlled water release </t>
+          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">FTF - Failure to function on demand </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Worn internal parts allow internal bypass flow </t>
+          <t xml:space="preserve">Corrosion-induced blockage or total obstruction </t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve internal condition verified by inspection? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Piping flush and flow verification performed [Y/N]; System acceptance test passed [Y/N] </t>
         </is>
       </c>
     </row>
@@ -3492,47 +2902,37 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Valve Failure</t>
+          <t>Piping Failure</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate water mist system sections for maintenance, testing, and controlled water release </t>
+          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">FTF - Failure to function on demand </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debris accumulation partially blocks valve flow path </t>
+          <t xml:space="preserve">Pipe rupture prevents pressurization and water delivery </t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve internals clean and free of debris? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Piping pressure integrity test performed [Y/N]; Piping replaced if rupture risk identified [Y/N] </t>
         </is>
       </c>
     </row>
@@ -3544,47 +2944,37 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Valve Failure</t>
+          <t>Piping Failure</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate water mist system sections for maintenance, testing, and controlled water release </t>
+          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">FTF - Failure to function on demand </t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1 Cavitation </t>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flashing across partially open valve creates noise </t>
+          <t xml:space="preserve">Section isolation valve inadvertently left closed after maintenance </t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve pressure ratio within design limits? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Piping section valve position verified open [Y/N]; Post-maintenance valve alignment check performed [Y/N] </t>
         </is>
       </c>
     </row>
@@ -3596,47 +2986,37 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Valve Failure</t>
+          <t>Valve Failure (*)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate water mist system sections for maintenance, testing, and controlled water release </t>
+          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">FTC - Failure to close on demand </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eroded trim creates turbulence noise </t>
+          <t xml:space="preserve">Debris prevents valve from fully closing </t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve trim condition verified? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Valve operation test performed - full close verified [Y/N]; Valve internals inspected for debris [Y/N] </t>
         </is>
       </c>
     </row>
@@ -3648,47 +3028,37 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Valve Failure</t>
+          <t>Valve Failure (*)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate water mist system sections for maintenance, testing, and controlled water release </t>
+          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">FTC - Failure to close on demand </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve stem sticking creates intermittent chatter noise </t>
+          <t xml:space="preserve">Corrosion on sealing surface prevents tight shut-off </t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve stem movement consistent during operation? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Valve seat/disk visual inspection performed [Y/N]; Valve leak test performed within limit [Y/N] </t>
         </is>
       </c>
     </row>
@@ -3700,47 +3070,37 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Power Supply Failure</t>
+          <t>Valve Failure (*)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deliver uninterrupted electrical power to water mist pump motor and control systems </t>
+          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTS - Failure to start on demand </t>
+          <t xml:space="preserve">FTC - Failure to close on demand </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 Open circuit </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circuit breaker tripped open prevents power delivery to system </t>
+          <t xml:space="preserve">Worn seat or disc prevents proper sealing </t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circuit breaker closed and latched? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Failure-Finding </t>
+          <t xml:space="preserve">Valve internal condition assessed for wear [Y/N]; Valve rebuild performed per schedule [Y/N] </t>
         </is>
       </c>
     </row>
@@ -3752,47 +3112,37 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Power Supply Failure</t>
+          <t>Valve Failure (*)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deliver uninterrupted electrical power to water mist pump motor and control systems </t>
+          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTS - Failure to start on demand </t>
+          <t xml:space="preserve">FTC - Failure to close on demand </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 No power/voltage </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loss of main or backup power supply to fire system </t>
+          <t xml:space="preserve">Valve seat deformed from overtightening or thermal stress </t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power supply availability verified? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Failure-Finding </t>
+          <t xml:space="preserve">Valve seat surface inspected for damage [Y/N]; Valve replaced if seat deformed [Y/N] </t>
         </is>
       </c>
     </row>
@@ -3804,47 +3154,37 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Power Supply Failure</t>
+          <t>Valve Failure (*)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deliver uninterrupted electrical power to water mist pump motor and control systems </t>
+          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTS - Failure to start on demand </t>
+          <t xml:space="preserve">FTO - Failure to open on demand </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">1.6 Sticking </t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose electrical connection at terminal interrupts power path </t>
+          <t xml:space="preserve">Stem seized or stuck due to corrosion or debris </t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrical terminal connections torque verified? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Valve operation exercised monthly [Y/N]; Valve stem lubrication performed [Y/N] </t>
         </is>
       </c>
     </row>
@@ -3856,47 +3196,37 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Power Supply Failure</t>
+          <t>Valve Failure (*)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deliver uninterrupted electrical power to water mist pump motor and control systems </t>
+          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOO - No output </t>
+          <t xml:space="preserve">FTO - Failure to open on demand </t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 No power/voltage </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power supply output zero due to internal converter failure </t>
+          <t xml:space="preserve">Corrosion buildup prevents valve from opening </t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power supply output voltage confirmed? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Failure-Finding </t>
+          <t xml:space="preserve">Valve full stroke test performed [Y/N]; Valve internal condition grade acceptable [Y/N] </t>
         </is>
       </c>
     </row>
@@ -3908,47 +3238,37 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Power Supply Failure</t>
+          <t>Valve Failure (*)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deliver uninterrupted electrical power to water mist pump motor and control systems </t>
+          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOO - No output </t>
+          <t xml:space="preserve">FTO - Failure to open on demand </t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">2.3 Erosion </t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blown fuse results in no output power to loads </t>
+          <t xml:space="preserve">Eroded seat prevents valve from fully opening </t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuses intact and proper rating confirmed? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Valve flow capacity test performed within limit [Y/N]; Valve seat replaced on condition [Y/N] </t>
         </is>
       </c>
     </row>
@@ -3960,47 +3280,37 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Power Supply Failure</t>
+          <t>Valve Failure (*)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deliver uninterrupted electrical power to water mist pump motor and control systems </t>
+          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOO - No output </t>
+          <t xml:space="preserve">FTO - Failure to open on demand </t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.1 Short circuiting </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internal short circuit collapses output voltage </t>
+          <t xml:space="preserve">Foreign material jams valve in closed position </t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power supply insulation resistance within limits? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Valve internal flush performed [Y/N]; Valve reassembled with new seals [Y/N] </t>
         </is>
       </c>
     </row>
@@ -4012,47 +3322,37 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Power Supply Failure</t>
+          <t>Valve Failure (*)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deliver uninterrupted electrical power to water mist pump motor and control systems </t>
+          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">FOV - Faulty output voltage </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 Faulty power/voltage </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Voltage regulator malfunction causes incorrect output voltage </t>
+          <t xml:space="preserve">Worn valve stem seals or packing leaks water </t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power supply output voltage within specified range? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Valve packing inspected and gland tightened [Y/N]; Valve stem condition acceptable [Y/N] </t>
         </is>
       </c>
     </row>
@@ -4064,47 +3364,37 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Power Supply Failure</t>
+          <t>Valve Failure (*)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deliver uninterrupted electrical power to water mist pump motor and control systems </t>
+          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">FOV - Faulty output voltage </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.4 Out of adjustment </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power supply calibration drifts from setpoint </t>
+          <t xml:space="preserve">Pinhole leak in valve body from corrosion </t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power supply calibration verified? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Valve body condition inspection performed [Y/N]; Valve replacement on condition [Y/N] </t>
         </is>
       </c>
     </row>
@@ -4116,47 +3406,37 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Power Supply Failure</t>
+          <t>Valve Failure (*)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deliver uninterrupted electrical power to water mist pump motor and control systems </t>
+          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">FOV - Faulty output voltage </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.1 Short circuiting </t>
+          <t xml:space="preserve">1.5 Looseness </t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial short circuit causes voltage deviation from nominal </t>
+          <t xml:space="preserve">Bonnet bolts loosened causing joint leak </t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power supply output ripple measured? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Valve bonnet bolt torque verified [Y/N]; Valve gasket condition inspected [Y/N] </t>
         </is>
       </c>
     </row>
@@ -4168,47 +3448,37 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Power Supply Failure</t>
+          <t>Valve Failure (*)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deliver uninterrupted electrical power to water mist pump motor and control systems </t>
+          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.1 Blockage/plugged </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling fan inlet blocked reduces heat dissipation from power supply </t>
+          <t xml:space="preserve">Fatigue crack in valve body at stress concentration points </t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power supply cooling fan operational? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Valve body surface crack detection performed [Y/N]; Valve replaced if crack found [Y/N] </t>
         </is>
       </c>
     </row>
@@ -4220,47 +3490,37 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Power Supply Failure</t>
+          <t>Valve Failure (*)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deliver uninterrupted electrical power to water mist pump motor and control systems </t>
+          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dust accumulation on heatsink reduces cooling efficiency </t>
+          <t xml:space="preserve">Internal corrosion restricts flow through partially closed valve </t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power supply heatsink clean and unobstructed? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Valve pressure drop test acceptable [Y/N]; Valve internal bore inspected for restrictions [Y/N] </t>
         </is>
       </c>
     </row>
@@ -4272,47 +3532,37 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Power Supply Failure</t>
+          <t>Valve Failure (*)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deliver uninterrupted electrical power to water mist pump motor and control systems </t>
+          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.1 Short circuiting </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internal partial short generates excess heat in power supply </t>
+          <t xml:space="preserve">Debris partially blocks valve bore </t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal protection device functional? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Valve flow test within acceptable range [Y/N]; Valve strainer inspected clean [Y/N] </t>
         </is>
       </c>
     </row>
@@ -4324,47 +3574,37 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Power Supply Failure</t>
+          <t>Valve Failure (*)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deliver uninterrupted electrical power to water mist pump motor and control systems </t>
+          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSF - Control/signal failure </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.4 Out of adjustment </t>
+          <t xml:space="preserve">2.3 Erosion </t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power supply control logic drifts affecting remote monitoring </t>
+          <t xml:space="preserve">Erosion enlarges flow path causing abnormal flow characteristic </t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power supply status signals correct? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive </t>
+          <t xml:space="preserve">Valve flow characteristic measured against design [Y/N]; Valve replaced if eroded [Y/N] </t>
         </is>
       </c>
     </row>
@@ -4376,47 +3616,37 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Power Supply Failure</t>
+          <t>Valve Failure (*)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deliver uninterrupted electrical power to water mist pump motor and control systems </t>
+          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSF - Control/signal failure </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 Open circuit </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication wire break prevents remote status monitoring </t>
+          <t xml:space="preserve">Valve body deformation from overstress changes internal geometry </t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remote monitoring communication link functional? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Failure-Finding </t>
+          <t xml:space="preserve">Valve body external inspection for deformation [Y/N]; Valve replaced if body distorted [Y/N] </t>
         </is>
       </c>
     </row>
@@ -4428,47 +3658,37 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Power Supply Failure</t>
+          <t>Valve Failure (*)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deliver uninterrupted electrical power to water mist pump motor and control systems </t>
+          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSF - Control/signal failure </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.3 Faulty signal/indication/alarm </t>
+          <t xml:space="preserve">1.6 Sticking </t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power supply status indicator shows incorrect state </t>
+          <t xml:space="preserve">Valve stuck in intermediate position due to corrosion or contamination </t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Status indicator condition verified? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Valve manual override tested [Y/N]; Valve actuating mechanism lubricated [Y/N] </t>
         </is>
       </c>
     </row>
@@ -4480,47 +3700,37 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Alarm Device Failure *</t>
+          <t>Valve Failure (*)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide audible and visual alert of water mist system activation, abnormal condition, or system fault </t>
+          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSF - Control/signal failure </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.2 No signal/indication/alarm </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication link loss prevents alarm activation </t>
+          <t xml:space="preserve">Corrosion binds valve internal mechanism preventing movement </t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alarm communication link functional? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Failure-Finding </t>
+          <t xml:space="preserve">Valve disassembled and cleaned per maintenance plan [Y/N]; Valve corrosion condition acceptable [Y/N] </t>
         </is>
       </c>
     </row>
@@ -4532,47 +3742,37 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Alarm Device Failure *</t>
+          <t>Valve Failure (*)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide audible and visual alert of water mist system activation, abnormal condition, or system fault </t>
+          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSF - Control/signal failure </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 Open circuit </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Broken alarm wiring interrupts signal path to annunciator </t>
+          <t xml:space="preserve">Foreign material jams valve mechanism </t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alarm wiring continuity verified? [Y/N] </t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive </t>
+          <t xml:space="preserve">Valve internal flush performed [Y/N]; Valve reassembled with new seals [Y/N] </t>
         </is>
       </c>
     </row>
@@ -4584,41 +3784,61 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate and distribute fine water mist to suppress fires by cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Alarm Device Failure *</t>
+          <t>Valve Failure (*)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide audible and visual alert of water mist system activation, abnormal condition, or system fault </t>
+          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSF - Control/signal failure </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.4 Out of adjustment </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alarm threshold misconfigured in PLC prevents normal alarm </t>
+          <t xml:space="preserve">Valve stem bent from overtorque preventing movement </t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Alarm threshold settings confirmed</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+          <t xml:space="preserve">Valve stem straightness check performed [Y/N]; Valve replaced if stem bent [Y/N] </t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Provide fire suppression by delivering water mist to extinguish or control fires through cooling,</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>nan *</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/EMS upgrade output - fire_fighting_system_water_mist.xlsx
+++ b/outputs/EMS upgrade output - fire_fighting_system_water_mist.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,26 +457,36 @@
           <t>Treatment Actions</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Reporting Question ID</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Treatment Action Type</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, displace oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cylinders Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -486,39 +496,49 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder body dented or bulging due to mechanical stress, potential for rupture </t>
+          <t xml:space="preserve">Loss of gas containment; system inoperable during fire </t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder visual inspection for shape distortion [Y/N]; Cylinder hydrostatic test performed per interval [Y/N] </t>
+          <t xml:space="preserve">External visual inspection for corrosion pitting performed? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, displace oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cylinders Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -528,39 +548,49 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Water/gas mixture leakage from cylinder wall or valve connection </t>
+          <t xml:space="preserve">Loss of gas containment; system inoperable during fire </t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder external visual corrosion inspection performed [Y/N]; Cylinder wall thickness measured within limit [Y/N] </t>
+          <t xml:space="preserve">Ultrasonic thickness measurement taken at critical stress areas? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, displace oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cylinders Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -570,39 +600,49 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stress crack in cylinder wall leads to leakage </t>
+          <t xml:space="preserve">Loss of gas containment; system inoperable during fire </t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder surface crack detection performed [Y/N]; Cylinder certification/requalification within interval [Y/N] </t>
+          <t xml:space="preserve">Support brackets and restraints checked for structural damage? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, displace oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cylinders Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -612,39 +652,49 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">2.3 Erosion </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catastrophic cylinder burst or rupture </t>
+          <t xml:space="preserve">Loss of gas containment; system inoperable during fire </t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder pressure relief device inspected [Y/N]; Cylinder within life cycle replacement schedule [Y/N] </t>
+          <t xml:space="preserve">Valve seat and internal stem area inspected for erosion damage? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, displace oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cylinders Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -654,39 +704,49 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Water quality or gas purity compromised affecting mist performance </t>
+          <t xml:space="preserve">Incorrect gas pressure; poor mist quality </t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Water sample tested per quality specification [Y/N]; Cylinder gas purity verified [Y/N] </t>
+          <t xml:space="preserve">Cylinder pressure gauge reading checked against required setpoint? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, displace oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cylinders Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -696,39 +756,49 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.4 Out of adjustment </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder pressure not at design setpoint </t>
+          <t xml:space="preserve">Incorrect gas pressure; poor mist quality </t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder pressure gauge reading within acceptable range [Y/N]; Pressure recorded vs specification [Y/N] </t>
+          <t xml:space="preserve">Gas supply pressure regulator function tested for proper output? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, displace oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cylinders Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -738,39 +808,49 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressure drop from temperature fluctuation affecting system readiness </t>
+          <t xml:space="preserve">Incorrect gas pressure; poor mist quality </t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ambient temperature in cylinder storage area within acceptable range [Y/N]; Cylinder temperature recorded [Y/N] </t>
+          <t xml:space="preserve">Cylinder hydrostatic test certificate verified as currently valid? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, displace oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cylinders Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -780,39 +860,49 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">6.2 Combined causes </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve seat wear allows slow gas leakage reducing pressure </t>
+          <t xml:space="preserve">Incorrect gas pressure; poor mist quality </t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder valve seat leakage test performed [Y/N]; Cylinder valve replaced if leaking [Y/N] </t>
+          <t xml:space="preserve">Gas pressure trend reviewed over last 3 months for drift? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, displace oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cylinders Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -827,34 +917,44 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">External corrosion reduces structural integrity over time </t>
+          <t xml:space="preserve">Loss of structural integrity of cylinder wall </t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder surface condition acceptable (no pitting/scaling) [Y/N]; Cylinder protective coating intact [Y/N] </t>
+          <t xml:space="preserve">Cylinder external visual inspection for dents/bulges/deformation? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, displace oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cylinders Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -864,39 +964,49 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damage from impact or mishandling </t>
+          <t xml:space="preserve">Loss of structural integrity of cylinder wall </t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder body free of dents and distortion [Y/N]; Cylinder mounting brackets secure and undamaged [Y/N] </t>
+          <t xml:space="preserve">Hydrostatic test performed at required 5-year interval? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, displace oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cylinders Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -911,34 +1021,44 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracking at mounting points or valve neck connection </t>
+          <t xml:space="preserve">Loss of structural integrity of cylinder wall </t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder mounting bracket inspection for cracks [Y/N]; Cylinder neck thread inspection performed [Y/N] </t>
+          <t xml:space="preserve">Support bracket and securing strap condition checked? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, displace oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cylinders Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -948,333 +1068,413 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crack propagation from corrosion or fatigue weakens cylinder wall </t>
+          <t xml:space="preserve">Loss of structural integrity of cylinder wall </t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder visual/dye-penetrant inspection for cracks [Y/N]; Cylinder replaced if structural defect found [Y/N] </t>
+          <t xml:space="preserve">Cylinder mounting base/foundation checked for distortion or settlement? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cylinders Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">FTO - Failure to open on demand </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">1.6 Sticking </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outlet valve blocked by debris preventing system discharge </t>
+          <t xml:space="preserve">Gas supply fails to activate during fire </t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder outlet valve function test performed [Y/N]; Cylinder discharge test on schedule [Y/N] </t>
+          <t xml:space="preserve">Cylinder isolation valve cycled to confirm full stroke open/close? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cylinders Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">FTO - Failure to open on demand </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve mechanism stuck preventing discharge </t>
+          <t xml:space="preserve">Gas supply fails to activate during fire </t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder valve manual operation test performed [Y/N]; Cylinder valve mechanism lubricated [Y/N] </t>
+          <t xml:space="preserve">Valve stem and actuator linkage free from corrosion build-up? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cylinders Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">FTO - Failure to open on demand </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">1.5 Looseness </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion seizes valve mechanism </t>
+          <t xml:space="preserve">Gas supply fails to activate during fire </t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder valve disassembled and inspected per interval [Y/N]; Cylinder replaced if valve seized [Y/N] </t>
+          <t xml:space="preserve">Valve actuator coupling bolts checked for tightness? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cylinders Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">FTO - Failure to open on demand </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">4.1 Short circuiting </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve seat wear causes internal bypass reducing discharge pressure </t>
+          <t xml:space="preserve">Gas supply fails to activate during fire </t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder valve seat condition inspected [Y/N]; Cylinder replaced if valve seat worn [Y/N] </t>
+          <t xml:space="preserve">Solenoid valve (if fitted) electrical continuity verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cylinders Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOO - No output </t>
+          <t xml:space="preserve">SPO - Spurious operation </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">6.3 Other </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder empty from undetected leakage through contamination-induced seal failure </t>
+          <t xml:space="preserve">Unintended gas release; system inoperable </t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder weight verification performed [Y/N]; Cylinder liquid level indicator inspected [Y/N] </t>
+          <t xml:space="preserve">Manual override/pull cable secured against accidental activation? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cylinders Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOO - No output </t>
+          <t xml:space="preserve">SPO - Spurious operation </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.4 Out of adjustment </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Insufficient pressure prevents discharge </t>
+          <t xml:space="preserve">Unintended gas release; system inoperable </t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder pressure gauged within acceptable range [Y/N]; Cylinder recharged if under pressure [Y/N] </t>
+          <t xml:space="preserve">Valve safety lock-off device confirmed operational? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cylinders Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOO - No output </t>
+          <t xml:space="preserve">SPO - Spurious operation </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve neck fracture prevents any discharge </t>
+          <t xml:space="preserve">Unintended gas release; system inoperable </t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder valve area visual inspection for cracks [Y/N]; Cylinder replaced if neck damaged [Y/N] </t>
+          <t xml:space="preserve">Cylinder protection cage/cover in place and intact? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cylinders Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store pressurized water and atomising gas mixture for system activation </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1284,1047 +1484,1297 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve stuck in closed position preventing discharge </t>
+          <t xml:space="preserve">No gas supply available when demanded </t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder valve operation test performed [Y/N]; Cylinder valve freed or replaced [Y/N] </t>
+          <t xml:space="preserve">Cylinder contents weighed (if applicable) to confirm fill level? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
+          <t xml:space="preserve">NOO - No output </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">1.6 Sticking </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle orifice blocked by debris or scale from piping </t>
+          <t xml:space="preserve">No gas supply available when demanded </t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle visual inspection for obstruction [Y/N]; Nozzle flow test performed within tolerance [Y/N] </t>
+          <t xml:space="preserve">Cylinder valve cap seal intact and undamaged? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Atomising Gas Cylinder Failure *</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
+          <t xml:space="preserve">Stores inert pressurised gas for water atomisation </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
+          <t xml:space="preserve">NOO - No output </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">5.1 Blockage/plugged </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion products obstruct nozzle orifice </t>
+          <t xml:space="preserve">No gas supply available when demanded </t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle material corrosion condition inspected [Y/N]; Nozzle replacement per interval program [Y/N] </t>
+          <t xml:space="preserve">Cylinder supply tube/pipe checked for obstructions? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Water Storage Cylinder Failure *</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
+          <t xml:space="preserve">Stores treated water for fire suppression system </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Droplet erosion enlarges/mis-shapes orifice affecting mist quality </t>
+          <t xml:space="preserve">Loss of water volume; reduced suppression capability </t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle discharge pattern tested per specification [Y/N]; Nozzle bore dimensions measured within limit [Y/N] </t>
+          <t xml:space="preserve">External visual inspection for corrosion pits performed? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Water Storage Cylinder Failure *</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
+          <t xml:space="preserve">Stores treated water for fire suppression system </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanical wear from aging/cycling degrades orifice geometry </t>
+          <t xml:space="preserve">Loss of water volume; reduced suppression capability </t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle dimensional check performed [Y/N]; Nozzle replacement scheduled [Y/N] </t>
+          <t xml:space="preserve">Tank supports and saddles checked for structural integrity? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Water Storage Cylinder Failure *</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
+          <t xml:space="preserve">Stores treated water for fire suppression system </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Droplet size distribution out of spec due to partial blockage </t>
+          <t xml:space="preserve">Loss of water volume; reduced suppression capability </t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle spray pattern observed and acceptable [Y/N]; Nozzle flow rate verified per datasheet [Y/N] </t>
+          <t xml:space="preserve">Weld integrity verified by NDT at required intervals? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Water Storage Cylinder Failure *</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
+          <t xml:space="preserve">Stores treated water for fire suppression system </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orifice enlargement from corrosion alters spray characteristics </t>
+          <t xml:space="preserve">Loss of water volume; reduced suppression capability </t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle corrosion grade condition acceptable [Y/N]; Nozzle inspected per manufacturer specification [Y/N] </t>
+          <t xml:space="preserve">Tank surface inspected for bulges or distortion? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Water Storage Cylinder Failure *</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
+          <t xml:space="preserve">Stores treated water for fire suppression system </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erosive wear changes spray angle or distribution pattern </t>
+          <t xml:space="preserve">Restricted flow from tank to pump; reduced suppression performance </t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle spray test conducted and passed [Y/N]; Nozzle replacement on condition [Y/N] </t>
+          <t xml:space="preserve">Tank drain valve opened to check for sediment buildup? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Water Storage Cylinder Failure *</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
+          <t xml:space="preserve">Stores treated water for fire suppression system </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paint or coating overspray obstructs nozzle opening </t>
+          <t xml:space="preserve">Restricted flow from tank to pump; reduced suppression performance </t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle visual check for external contamination [Y/N]; Nozzle protective cap in place (where fitted) [Y/N] </t>
+          <t xml:space="preserve">Tank outlet strainer inspected and cleaned? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Water Storage Cylinder Failure *</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
+          <t xml:space="preserve">Stores treated water for fire suppression system </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical damage from impact, heat, or corrosion </t>
+          <t xml:space="preserve">Restricted flow from tank to pump; reduced suppression performance </t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle body free of cracks and deformation [Y/N]; Nozzle mounting secure [Y/N] </t>
+          <t xml:space="preserve">Tank vent vacuum breaker checked for correct operation? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Water Storage Cylinder Failure *</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
+          <t xml:space="preserve">Stores treated water for fire suppression system </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.3 Erosion </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion weakens nozzle body structure </t>
+          <t xml:space="preserve">Restricted flow from tank to pump; reduced suppression performance </t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle condition grade acceptable [Y/N]; Nozzle replaced per maintenance schedule [Y/N] </t>
+          <t xml:space="preserve">Tank internal baffles (if fitted) inspected for damage? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Water Storage Cylinder Failure *</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
+          <t xml:space="preserve">Stores treated water for fire suppression system </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracking at nozzle-to-piping connection due to vibration </t>
+          <t xml:space="preserve">Water quality degraded; potential nozzle blockage </t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle connection inspected for cracks [Y/N]; Nozzle support bracket secure [Y/N] </t>
+          <t xml:space="preserve">Water sample taken for conductivity and particulate analysis? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Water Storage Cylinder Failure *</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
+          <t xml:space="preserve">Stores treated water for fire suppression system </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thread wear on nozzle body from repeated assembly/disassembly </t>
+          <t xml:space="preserve">Water quality degraded; potential nozzle blockage </t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle thread condition inspected [Y/N]; Nozzle replaced if thread worn [Y/N] </t>
+          <t xml:space="preserve">Tank internal coating condition verified as intact? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Water Storage Cylinder Failure *</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
+          <t xml:space="preserve">Stores treated water for fire suppression system </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">6.2 Combined causes </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Water leak at nozzle-to-piping threaded connection from corrosion </t>
+          <t xml:space="preserve">Water level low; pump starved </t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle connection inspected for leakage [Y/N]; Joint seals/gaskets condition checked [Y/N] </t>
+          <t xml:space="preserve">Water level confirmed at required level using local gauge? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Water Storage Cylinder Failure *</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
+          <t xml:space="preserve">Stores treated water for fire suppression system </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle not fully tightened or seal degraded </t>
+          <t xml:space="preserve">Water level low; pump starved </t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle torque check performed [Y/N]; Nozzle seal/gasket replaced if degraded [Y/N] </t>
+          <t xml:space="preserve">Tank fill valve checked for correct automatic operation? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Water Storage Cylinder Failure *</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
+          <t xml:space="preserve">Stores treated water for fire suppression system </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thread damage from overtightening or cross-threading causes leak </t>
+          <t xml:space="preserve">Loss of structural integrity of tank </t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle thread condition inspected [Y/N]; Nozzle replaced if damaged [Y/N] </t>
+          <t xml:space="preserve">Tank shell minimum thickness verified by UT? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Water Storage Cylinder Failure *</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
+          <t xml:space="preserve">Stores treated water for fire suppression system </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thread wear from repeated assembly/disassembly causes leak path </t>
+          <t xml:space="preserve">Loss of structural integrity of tank </t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle replacement scheduled based on wear assessment [Y/N]; Spare nozzle available [Y/N] </t>
+          <t xml:space="preserve">Foundation and anchor bolts checked for tightness? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Water Storage Cylinder Failure *</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
+          <t xml:space="preserve">Stores treated water for fire suppression system </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle fails to discharge due to obstruction from debris </t>
+          <t xml:space="preserve">Loss of structural integrity of tank </t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">System activation test performed - nozzle discharge verified [Y/N]; Nozzle obstruction check performed [Y/N] </t>
+          <t xml:space="preserve">Tank shell and weld lines visually inspected for cracking? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Water Storage Cylinder Failure *</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
+          <t xml:space="preserve">Stores treated water for fire suppression system </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion seizes nozzle internal moving parts (fusible link or release mechanism) </t>
+          <t xml:space="preserve">Loss of structural integrity of tank </t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle movement/freedom test performed [Y/N]; Nozzle replaced if seized [Y/N] </t>
+          <t xml:space="preserve">Tank foundation checked for settlement or cracking? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Water Storage Cylinder Failure *</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
+          <t xml:space="preserve">Stores treated water for fire suppression system </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">FTI - Failure to function as intended </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paint or coating buildup prevents nozzle activation </t>
+          <t xml:space="preserve">Water supply insufficient or blocked </t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle activation test performed per schedule [Y/N]; Nozzle protective cap condition verified [Y/N] </t>
+          <t xml:space="preserve">Water quality analysis performed per maintenance schedule? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nozzle Failure</t>
+          <t>Water Storage Cylinder Failure *</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispense fine water droplets (mist) into protected area for fire suppression </t>
+          <t xml:space="preserve">Stores treated water for fire suppression system </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">FTI - Failure to function as intended </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+          <t xml:space="preserve">1.6 Sticking </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanical damage (impact) deforms nozzle preventing discharge </t>
+          <t xml:space="preserve">Water supply insufficient or blocked </t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nozzle physical condition inspected [Y/N]; Nozzle replaced if damaged [Y/N] </t>
+          <t xml:space="preserve">Tank isolation valve operation stroked fully? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Piping Failure</t>
+          <t>Water Storage Cylinder Failure *</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
+          <t xml:space="preserve">Stores treated water for fire suppression system </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">FTI - Failure to function as intended </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pinhole leak from external or internal corrosion </t>
+          <t xml:space="preserve">Water supply insufficient or blocked </t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping visual inspection for corrosion damage performed [Y/N]; Piping wall thickness (UT) measured within limit [Y/N] </t>
+          <t xml:space="preserve">Tank level transmitter calibration verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Piping Failure</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibration-induced fatigue crack at supports or fittings </t>
+          <t xml:space="preserve">Loss of spray pattern; reduced suppression effectiveness </t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping supports/brackets inspected for damage [Y/N]; Piping vibration dampeners effective [Y/N] </t>
+          <t xml:space="preserve">Nozzle orifice visually inspected for debris/blockage? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Piping Failure</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flange or fitting loosened causing leak at joint </t>
+          <t xml:space="preserve">Loss of spray pattern; reduced suppression effectiveness </t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flange bolts torque checked [Y/N]; Joint gaskets inspected for condition [Y/N] </t>
+          <t xml:space="preserve">Nozzle body checked for corrosion build-up at orifice? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Piping Failure</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">2.3 Erosion </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pipe rupture due to overpressure or freeze damage </t>
+          <t xml:space="preserve">Loss of spray pattern; reduced suppression effectiveness </t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping pressure test performed per interval [Y/N]; Freeze protection (trace heating/insulation) operational [Y/N] </t>
+          <t xml:space="preserve">Nozzle flow test performed to confirm discharge pattern? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Piping Failure</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2334,837 +2784,1037 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sediment or scale buildup in piping restricts flow </t>
+          <t xml:space="preserve">Loss of spray pattern; reduced suppression effectiveness </t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping flush performed per maintenance schedule [Y/N]; System strainer inspected clean [Y/N] </t>
+          <t xml:space="preserve">Nozzle removed and flow tested per maintenance schedule? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Piping Failure</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foreign object or construction debris obstructs piping </t>
+          <t xml:space="preserve">Nozzle physically degraded; spray pattern lost </t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping borescope inspection performed for obstructions [Y/N]; Flow test performed and acceptable [Y/N] </t>
+          <t xml:space="preserve">Nozzle body and cap free from corrosion and damage? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Piping Failure</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion buildup (tuberculation) narrows pipe bore restricting flow </t>
+          <t xml:space="preserve">Nozzle physically degraded; spray pattern lost </t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping internal condition assessed per schedule [Y/N]; Piping replacement on condition [Y/N] </t>
+          <t xml:space="preserve">Nozzle impact shield (if fitted) in place and undamaged? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Piping Failure</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLU - Plugged/choked </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erosion debris trapped at restrictions creates partial blockages </t>
+          <t xml:space="preserve">Nozzle physically degraded; spray pattern lost </t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping internal inspection at low points performed [Y/N]; Piping drain/flush valve exercised [Y/N] </t>
+          <t xml:space="preserve">Nozzle material condition checked for throat/orifice wear? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Piping Failure</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internal corrosion increases surface roughness reducing flow capacity </t>
+          <t xml:space="preserve">Nozzle physically degraded; spray pattern lost </t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flow test conducted within acceptable limit [Y/N]; Piping internal corrosion assessment performed [Y/N] </t>
+          <t xml:space="preserve">Nozzle thread/connection checked for damage or distortion? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Piping Failure</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">SPO - Spurious operation </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erosion at bends or restrictions alters flow characteristics </t>
+          <t xml:space="preserve">Unwanted water release; water damage and system activation </t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping wall thickness at bends measured [Y/N]; Piping replacement scheduled based on UT readings [Y/N] </t>
+          <t xml:space="preserve">Nozzle heat-sensitive element (bulb/link) visually inspected? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Piping Failure</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">SPO - Spurious operation </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scale/deposit buildup increases friction loss reducing flow </t>
+          <t xml:space="preserve">Unwanted water release; water damage and system activation </t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Water quality test performed - acceptable [Y/N]; Pipe cleaning/flush performed per interval [Y/N] </t>
+          <t xml:space="preserve">Nozzle protective cap (if fitted) checked as intact? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Piping Failure</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">SPO - Spurious operation </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">6.3 Other </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kinked or crushed pipe reduces cross-section area </t>
+          <t xml:space="preserve">Unwanted water release; water damage and system activation </t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping visual inspection for kinks/flattened sections [Y/N]; Piping replaced if deformed [Y/N] </t>
+          <t xml:space="preserve">Ambient temperature in nozzle area confirmed below activation temp? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Piping Failure</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">SPO - Spurious operation </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">External corrosion weakens pipe wall structural integrity </t>
+          <t xml:space="preserve">Unwanted water release; water damage and system activation </t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping external surface condition acceptable [Y/N]; Protective coating condition acceptable [Y/N] </t>
+          <t xml:space="preserve">Nozzle heat-responsive element expiry date verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Piping Failure</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">FTI - Failure to function as intended </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dents or mechanical damage from impact </t>
+          <t xml:space="preserve">Nozzle fails to activate or provides limited flow </t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping inspection for mechanical damage performed [Y/N]; Piping supports and clamps inspected [Y/N] </t>
+          <t xml:space="preserve">Nozzle internal strainer (if fitted) cleaned? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Piping Failure</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">FTI - Failure to function as intended </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanical fatigue at support points from vibration </t>
+          <t xml:space="preserve">Nozzle fails to activate or provides limited flow </t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping hanger/support condition inspected [Y/N]; Pipe clamp torque verified [Y/N] </t>
+          <t xml:space="preserve">Nozzle alignment and orientation in head verified as correct? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Piping Failure</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">FTI - Failure to function as intended </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Complete pipe fracture due to overstress or corrosion </t>
+          <t xml:space="preserve">Nozzle fails to activate or provides limited flow </t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping pressure integrity test performed [Y/N]; Piping replaced if crack or fracture found [Y/N] </t>
+          <t xml:space="preserve">Fusible link (if fitted) condition and continuity verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Piping Failure</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">FTI - Failure to function as intended </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">1.6 Sticking </t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obstruction prevents water flow during activation </t>
+          <t xml:space="preserve">Nozzle fails to activate or provides limited flow </t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">System discharge test performed - flow verified to all zones [Y/N]; Piping section isolation tested [Y/N] </t>
+          <t xml:space="preserve">Nozzle valve pin (if applicable) free movement checked? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Piping Failure</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion-induced blockage or total obstruction </t>
+          <t xml:space="preserve">Nozzle spray pattern degraded; poor suppression </t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping flush and flow verification performed [Y/N]; System acceptance test passed [Y/N] </t>
+          <t xml:space="preserve">Flow test of nozzle branch performed annually? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Piping Failure</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">2.3 Erosion </t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pipe rupture prevents pressurization and water delivery </t>
+          <t xml:space="preserve">Nozzle spray pattern degraded; poor suppression </t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping pressure integrity test performed [Y/N]; Piping replaced if rupture risk identified [Y/N] </t>
+          <t xml:space="preserve">Nozzle orifice diameter measured against spec? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Piping Failure</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribute pressurized water/gas from cylinders to nozzles throughout protected area </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTF - Failure to function on demand </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section isolation valve inadvertently left closed after maintenance </t>
+          <t xml:space="preserve">Nozzle spray pattern degraded; poor suppression </t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piping section valve position verified open [Y/N]; Post-maintenance valve alignment check performed [Y/N] </t>
+          <t xml:space="preserve">Nozzle replaced per maintenance schedule? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Valve Failure (*)</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTC - Failure to close on demand </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">2.1 Cavitation </t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debris prevents valve from fully closing </t>
+          <t xml:space="preserve">Unusual operating sound indicating cavitation damage </t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve operation test performed - full close verified [Y/N]; Valve internals inspected for debris [Y/N] </t>
+          <t xml:space="preserve">Nozzle noise level checked during flow test? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Valve Failure (*)</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTC - Failure to close on demand </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.3 Erosion </t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion on sealing surface prevents tight shut-off </t>
+          <t xml:space="preserve">Unusual operating sound indicating erosion </t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve seat/disk visual inspection performed [Y/N]; Valve leak test performed within limit [Y/N] </t>
+          <t xml:space="preserve">Nozzle upstream pressure measured for cavitation margin? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Valve Failure (*)</t>
+          <t>Water Mist Nozzle Failure *</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
+          <t xml:space="preserve">Discharges fine water spray for fire suppression </t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTC - Failure to close on demand </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Worn seat or disc prevents proper sealing </t>
+          <t xml:space="preserve">Unusual operating sound indicating debris </t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve internal condition assessed for wear [Y/N]; Valve rebuild performed per schedule [Y/N] </t>
+          <t xml:space="preserve">Nozzle replaced if abnormal noise is present during test? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run-to-Failure </t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Valve Failure (*)</t>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTC - Failure to close on demand </t>
+          <t xml:space="preserve">FTO - Failure to open on demand </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">1.6 Sticking </t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve seat deformed from overtightening or thermal stress </t>
+          <t xml:space="preserve">No water release to fire zone </t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve seat surface inspected for damage [Y/N]; Valve replaced if seat deformed [Y/N] </t>
+          <t xml:space="preserve">Nozzle stem valve tested for full stroke opening? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Valve Failure (*)</t>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3174,39 +3824,49 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stem seized or stuck due to corrosion or debris </t>
+          <t xml:space="preserve">No water release to fire zone </t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve operation exercised monthly [Y/N]; Valve stem lubrication performed [Y/N] </t>
+          <t xml:space="preserve">Stem/valve visual inspection for corrosion or deposits? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Valve Failure (*)</t>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3216,39 +3876,49 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">1.5 Looseness </t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion buildup prevents valve from opening </t>
+          <t xml:space="preserve">No water release to fire zone </t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve full stroke test performed [Y/N]; Valve internal condition grade acceptable [Y/N] </t>
+          <t xml:space="preserve">Actuator linkage connection to valve stem verified secure? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Valve Failure (*)</t>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3258,81 +3928,101 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eroded seat prevents valve from fully opening </t>
+          <t xml:space="preserve">No water release to fire zone </t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve flow capacity test performed within limit [Y/N]; Valve seat replaced on condition [Y/N] </t>
+          <t xml:space="preserve">Valve internal strainer (if fitted) inspected and cleaned? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Valve Failure (*)</t>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTO - Failure to open on demand </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foreign material jams valve in closed position </t>
+          <t xml:space="preserve">Water leakage from stem seal; pressure loss </t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve internal flush performed [Y/N]; Valve reassembled with new seals [Y/N] </t>
+          <t xml:space="preserve">Stem seal/packing system inspected for signs of leakage? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Valve Failure (*)</t>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3342,39 +4032,49 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Worn valve stem seals or packing leaks water </t>
+          <t xml:space="preserve">Water leakage from stem seal; pressure loss </t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve packing inspected and gland tightened [Y/N]; Valve stem condition acceptable [Y/N] </t>
+          <t xml:space="preserve">Valve external body and connections checked for pitting? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Valve Failure (*)</t>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3384,39 +4084,49 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pinhole leak in valve body from corrosion </t>
+          <t xml:space="preserve">Water leakage from stem seal; pressure loss </t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve body condition inspection performed [Y/N]; Valve replacement on condition [Y/N] </t>
+          <t xml:space="preserve">Flange bolts tightened to correct torque verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Valve Failure (*)</t>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3426,128 +4136,158 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bonnet bolts loosened causing joint leak </t>
+          <t xml:space="preserve">Water leakage from stem seal; pressure loss </t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve bonnet bolt torque verified [Y/N]; Valve gasket condition inspected [Y/N] </t>
+          <t xml:space="preserve">Valve bonnet/body joint gasket condition checked? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Valve Failure (*)</t>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue crack in valve body at stress concentration points </t>
+          <t xml:space="preserve">Valve seized; cannot open or close </t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve body surface crack detection performed [Y/N]; Valve replaced if crack found [Y/N] </t>
+          <t xml:space="preserve">Valve stem manually stroked to confirm free movement? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Valve Failure (*)</t>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">1.6 Sticking </t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internal corrosion restricts flow through partially closed valve </t>
+          <t xml:space="preserve">Valve seized; cannot open or close </t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve pressure drop test acceptable [Y/N]; Valve internal bore inspected for restrictions [Y/N] </t>
+          <t xml:space="preserve">Anti-seize compound applied to stem threads (if applicable)? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Valve Failure (*)</t>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3557,76 +4297,96 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debris partially blocks valve bore </t>
+          <t xml:space="preserve">Valve seized; cannot open or close </t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve flow test within acceptable range [Y/N]; Valve strainer inspected clean [Y/N] </t>
+          <t xml:space="preserve">Valve internals flushed after installation/maintenance? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Valve Failure (*)</t>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">STU - Stuck </t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erosion enlarges flow path causing abnormal flow characteristic </t>
+          <t xml:space="preserve">Valve seized; cannot open or close </t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve flow characteristic measured against design [Y/N]; Valve replaced if eroded [Y/N] </t>
+          <t xml:space="preserve">Valve body/seat area checked for mechanical distortion? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Valve Failure (*)</t>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3636,170 +4396,210 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve body deformation from overstress changes internal geometry </t>
+          <t xml:space="preserve">Valve not seating properly; internal leakage </t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve body external inspection for deformation [Y/N]; Valve replaced if body distorted [Y/N] </t>
+          <t xml:space="preserve">Valve seat area integrity verified by leak test? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding </t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Valve Failure (*)</t>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">STU - Stuck </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve stuck in intermediate position due to corrosion or contamination </t>
+          <t xml:space="preserve">Valve not seating properly; internal leakage </t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve manual override tested [Y/N]; Valve actuating mechanism lubricated [Y/N] </t>
+          <t xml:space="preserve">Valve seat surface inspected for pitting or distortion? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Valve Failure (*)</t>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">STU - Stuck </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion binds valve internal mechanism preventing movement </t>
+          <t xml:space="preserve">Valve not seating properly; internal leakage </t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve disassembled and cleaned per maintenance plan [Y/N]; Valve corrosion condition acceptable [Y/N] </t>
+          <t xml:space="preserve">Seat/seal area inspected for debris build-up? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Valve Failure (*)</t>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">STU - Stuck </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foreign material jams valve mechanism </t>
+          <t xml:space="preserve">Valve not seating properly; internal leakage </t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve internal flush performed [Y/N]; Valve reassembled with new seals [Y/N] </t>
+          <t xml:space="preserve">Valve soft seals (elastomers) checked for degradation? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide fire suppression by delivering water mist to extinguish or control fires through cooling, oxygen displacement, and radiant heat attenuation </t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Valve Failure (*)</t>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isolate system sections, allow refill, and control flow direction </t>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">STU - Stuck </t>
+          <t xml:space="preserve">FTI - Failure to function as intended </t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3809,36 +4609,536 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve stem bent from overtorque preventing movement </t>
+          <t xml:space="preserve">Valve opens slow or partially; delayed suppression </t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve stem straightness check performed [Y/N]; Valve replaced if stem bent [Y/N] </t>
+          <t xml:space="preserve">Actuator pressure/flow supply checked for meeting valve demand? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEWM - Fire Fighting System, Water Mist </t>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Provide fire suppression by delivering water mist to extinguish or control fires through cooling,</t>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>nan *</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FTI - Failure to function as intended </t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.4 Wear </t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valve opens slow or partially; delayed suppression </t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valve operating time measured against specification? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding </t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FTI - Failure to function as intended </t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.6 Sticking </t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valve opens slow or partially; delayed suppression </t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valve lubrication points serviced at required interval? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FTI - Failure to function as intended </t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valve opens slow or partially; delayed suppression </t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valve stem shaft diameter checked for corrosion build-up? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SLL - Spurious low alarm level </t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">False low flow alarm; loss of confidence in system </t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valve limit switch (if fitted) free from corrosion and alignment checked? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SLL - Spurious low alarm level </t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.4 Out of adjustment </t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">False low flow alarm; loss of confidence in system </t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valve position sensor/indicator calibration verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Nozzle Assembly Stem/Valve Failure *</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Controls water release from header to nozzle </t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SLL - Spurious low alarm level </t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2 Contamination </t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">False low flow alarm; loss of confidence in system </t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Limit switch sensing surface inspected for debris? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Atomising Gas Control Valve Failure *</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regulates flow of atomising gas from cylinder source </t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FTO - Failure to open on demand </t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.6 Sticking </t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gas not supplied for atomisation; water mist not formed </t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valve stem manually cycled to confirm free stroke? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding </t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Atomising Gas Control Valve Failure *</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regulates flow of atomising gas from cylinder source </t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FTO - Failure to open on demand </t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gas not supplied for atomisation; water mist not formed </t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valve internal spring/seat inspected for corrosion? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Atomising Gas Control Valve Failure *</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regulates flow of atomising gas from cylinder source </t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FTO - Failure to open on demand </t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5 Looseness </t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gas not supplied for atomisation; water mist not formed </t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actuator coupling and linkage alignment verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fire Fighting System, Water Mist </t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide fire suppression using fine water spray to cool, disperse oxygen, and attenuate radiant heat. </t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Atomising Gas Control Valve Failure *</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regulates flow of atomising gas from cylinder source </t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FTO - Failure to open on demand </t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 Short circuiting </t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gas not supplied for atomisation; water mist not formed </t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Solenoid operator (if fitted) electrical supply checked? [Y/N]</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
